--- a/release_1_0_0/data/files/input/hotel_clients.xlsx
+++ b/release_1_0_0/data/files/input/hotel_clients.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="hotel_clients" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,84 +488,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H6188</t>
+          <t>HB5I0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mercure Paris Boulogne</t>
+          <t>Novotel Megève Mont-Blanc</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>191</v>
+        <v>572</v>
       </c>
       <c r="D4" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HB5I0</t>
+          <t>H0373</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Novotel Megève Mont-Blanc</t>
+          <t>Mercure Paris Montmartre Sacré-Cœur</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>572</v>
+        <v>305</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H0373</t>
+          <t>H3546</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mercure Paris Montmartre Sacré-Cœur</t>
+          <t>Novotel Paris Centre Tour Eiffel</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>764</v>
       </c>
       <c r="D6" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>H3546</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Novotel Paris Centre Tour Eiffel</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>764</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E7" t="n">
         <v>1.8</v>
       </c>
     </row>
